--- a/data/analysis_panns/sound_event_eval_panns_w1_0s_h1_0s.xlsx
+++ b/data/analysis_panns/sound_event_eval_panns_w1_0s_h1_0s.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="30">
   <si>
     <t>event</t>
   </si>
@@ -81,49 +81,43 @@
     <t>NO</t>
   </si>
   <si>
-    <t>speech(0-48), animal(48-144), music(72-96), music(144-168), silence(168-192), engine(192-240)</t>
-  </si>
-  <si>
-    <t>speech(0-168), music(168-216), engine(216-240)</t>
-  </si>
-  <si>
-    <t>speech(0-120), engine(120-240)</t>
+    <t>engine(192-240)</t>
+  </si>
+  <si>
+    <t>engine(216-240)</t>
+  </si>
+  <si>
+    <t>engine(120-240)</t>
   </si>
   <si>
     <t>YES</t>
   </si>
   <si>
-    <t>speech(0-96), burst_pop(96-120), gunshot_or_explosion(120-144), engine(144-240)</t>
-  </si>
-  <si>
-    <t>engine(0-48), door(48-72), gunshot_or_explosion(72-96), speech(96-120), engine(120-240), music(144-216)</t>
-  </si>
-  <si>
-    <t>silence(0-24), engine(24-72), speech(72-120), gunshot_or_explosion(120-144), engine(144-240), music(168-192)</t>
-  </si>
-  <si>
-    <t>music(0-24), engine(24-240)</t>
-  </si>
-  <si>
-    <t>engine(0-24), music(24-48), gunshot_or_explosion(48-72), engine(72-240), speech(120-144)</t>
-  </si>
-  <si>
-    <t>engine(0-240), silence(24-48), music(72-96)</t>
-  </si>
-  <si>
-    <t>music(0-48), engine(48-240)</t>
+    <t>gunshot_or_explosion(96-144), engine(144-240)</t>
+  </si>
+  <si>
+    <t>engine(0-48), gunshot_or_explosion(72-96), engine(120-240)</t>
+  </si>
+  <si>
+    <t>engine(24-72), gunshot_or_explosion(120-144), engine(144-240)</t>
+  </si>
+  <si>
+    <t>engine(24-240)</t>
+  </si>
+  <si>
+    <t>engine(0-24), gunshot_or_explosion(48-72), engine(72-240)</t>
   </si>
   <si>
     <t>engine(0-240)</t>
   </si>
   <si>
-    <t>engine(0-240), horn(24-48), music(72-96), music(192-216)</t>
-  </si>
-  <si>
-    <t>engine(0-144), speech(144-216), engine(216-240)</t>
-  </si>
-  <si>
-    <t>engine(0-240), music(72-96), silence(168-192)</t>
+    <t>engine(48-240)</t>
+  </si>
+  <si>
+    <t>engine(0-240), horn(24-48)</t>
+  </si>
+  <si>
+    <t>engine(0-144), engine(216-240)</t>
   </si>
 </sst>
 </file>
@@ -743,6 +737,50 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>28</v>
       </c>
     </row>
@@ -751,31 +789,31 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>15</v>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>16</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -795,35 +833,343 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>10</v>
       </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
       <c r="C2" t="s">
         <v>16</v>
       </c>
@@ -831,401 +1177,49 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>17</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
       <c r="E2" t="s">
         <v>25</v>
       </c>

--- a/data/analysis_panns/sound_event_eval_panns_w1_0s_h1_0s.xlsx
+++ b/data/analysis_panns/sound_event_eval_panns_w1_0s_h1_0s.xlsx
@@ -22,13 +22,19 @@
     <sheet name="Scene_15" sheetId="13" r:id="rId13"/>
     <sheet name="Scene_16" sheetId="14" r:id="rId14"/>
     <sheet name="Scene_17" sheetId="15" r:id="rId15"/>
+    <sheet name="Scene_29" sheetId="16" r:id="rId16"/>
+    <sheet name="Scene_30" sheetId="17" r:id="rId17"/>
+    <sheet name="Scene_31" sheetId="18" r:id="rId18"/>
+    <sheet name="Scene_32" sheetId="19" r:id="rId19"/>
+    <sheet name="Scene_33" sheetId="20" r:id="rId20"/>
+    <sheet name="Scene_34" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="35">
   <si>
     <t>event</t>
   </si>
@@ -118,6 +124,21 @@
   </si>
   <si>
     <t>engine(0-144), engine(216-240)</t>
+  </si>
+  <si>
+    <t>engine(96-240)</t>
+  </si>
+  <si>
+    <t>engine(0-24), engine(72-240)</t>
+  </si>
+  <si>
+    <t>engine(0-24), horn(24-72), engine(72-216)</t>
+  </si>
+  <si>
+    <t>engine(0-48), gunshot_or_explosion(48-72), engine(120-168)</t>
+  </si>
+  <si>
+    <t>engine(0-48), engine(120-168), gunshot_or_explosion(48-72)</t>
   </si>
 </sst>
 </file>
@@ -877,6 +898,176 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
@@ -921,6 +1112,111 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
